--- a/data/trans_dic/IP16A11_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor</t>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,53; 57,55</t>
+          <t>25,89; 56,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,8; 61,16</t>
+          <t>30,76; 63,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,43; 54,56</t>
+          <t>32,7; 56,24</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,35; 52,83</t>
+          <t>21,38; 53,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,59; 49,19</t>
+          <t>15,77; 51,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,64; 47,85</t>
+          <t>23,17; 46,19</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 67,39</t>
+          <t>15,54; 64,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 50,54</t>
+          <t>12,01; 51,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 48,89</t>
+          <t>18,04; 47,54</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 43,15</t>
+          <t>8,05; 41,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 39,84</t>
+          <t>19,02; 39,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,81; 36,0</t>
+          <t>13,53; 35,87</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,79; 53,86</t>
+          <t>25,02; 54,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 45,46</t>
+          <t>17,79; 46,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,52; 45,2</t>
+          <t>24,13; 43,62</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,94; 60,16</t>
+          <t>16,5; 58,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,71; 61,38</t>
+          <t>15,74; 64,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,47; 51,8</t>
+          <t>20,91; 52,13</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,99; 41,7</t>
+          <t>19,24; 41,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,57; 39,66</t>
+          <t>26,58; 39,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,13; 37,23</t>
+          <t>24,22; 37,51</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10365</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14642</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6435; 14047</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9815; 20165</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18564; 31922</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7317</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15929</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5009; 12557</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3704; 11999</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10871; 21674</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8566</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1491; 6148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2077; 8830</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4853; 12784</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>18631</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15502</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34133</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6227; 32302</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10624; 22113</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18016; 47765</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11461</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10779</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22240</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7406; 16021</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6402; 16683</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15824; 28601</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>4230</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5468</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9698</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2017; 7139</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2408; 9924</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5754; 14347</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>57005</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>58569</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>115574</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>34062; 74311</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>47792; 70992</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>86433; 133837</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A11_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,89; 56,52</t>
+          <t>25,45; 57,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,76; 63,19</t>
+          <t>30,53; 62,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,7; 56,24</t>
+          <t>33,63; 55,26</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,38; 53,59</t>
+          <t>22,47; 54,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,77; 51,08</t>
+          <t>16,26; 51,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,17; 46,19</t>
+          <t>23,68; 46,06</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,54; 64,07</t>
+          <t>16,66; 65,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,01; 51,05</t>
+          <t>11,15; 54,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 47,54</t>
+          <t>17,55; 49,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 41,77</t>
+          <t>7,87; 41,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,02; 39,6</t>
+          <t>16,78; 37,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 35,87</t>
+          <t>12,66; 36,98</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,02; 54,14</t>
+          <t>24,82; 55,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 46,37</t>
+          <t>17,19; 45,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,13; 43,62</t>
+          <t>24,77; 44,67</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,5; 58,41</t>
+          <t>13,0; 58,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,74; 64,87</t>
+          <t>15,88; 63,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,91; 52,13</t>
+          <t>19,9; 53,97</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,24; 41,98</t>
+          <t>19,67; 40,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,58; 39,48</t>
+          <t>27,14; 39,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,22; 37,51</t>
+          <t>24,73; 37,66</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6435; 14047</t>
+          <t>6324; 14177</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9815; 20165</t>
+          <t>9741; 19894</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18564; 31922</t>
+          <t>19088; 31364</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5009; 12557</t>
+          <t>5265; 12843</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3704; 11999</t>
+          <t>3819; 12119</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10871; 21674</t>
+          <t>11112; 21615</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1491; 6148</t>
+          <t>1598; 6244</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2077; 8830</t>
+          <t>1929; 9362</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4853; 12784</t>
+          <t>4719; 13428</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6227; 32302</t>
+          <t>6090; 32432</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10624; 22113</t>
+          <t>9370; 20952</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18016; 47765</t>
+          <t>16857; 49245</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7406; 16021</t>
+          <t>7347; 16339</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6402; 16683</t>
+          <t>6183; 16322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15824; 28601</t>
+          <t>16241; 29294</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2017; 7139</t>
+          <t>1589; 7185</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2408; 9924</t>
+          <t>2430; 9679</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5754; 14347</t>
+          <t>5476; 14853</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34062; 74311</t>
+          <t>34824; 72420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>47792; 70992</t>
+          <t>48794; 70461</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>86433; 133837</t>
+          <t>88258; 134394</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Clase-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,45; 57,05</t>
+          <t>30,4; 61,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,53; 62,35</t>
+          <t>26,76; 58,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,63; 55,26</t>
+          <t>32,62; 55,39</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,47; 54,81</t>
+          <t>15,6; 49,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 51,59</t>
+          <t>22,11; 54,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,68; 46,06</t>
+          <t>23,13; 48,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 65,07</t>
+          <t>11,93; 53,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 54,13</t>
+          <t>18,75; 69,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,55; 49,93</t>
+          <t>19,9; 51,58</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 41,94</t>
+          <t>15,65; 36,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 37,52</t>
+          <t>27,96; 52,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 36,98</t>
+          <t>24,37; 41,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,82; 55,21</t>
+          <t>18,16; 48,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 45,37</t>
+          <t>23,9; 55,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,77; 44,67</t>
+          <t>25,39; 46,68</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,0; 58,79</t>
+          <t>14,85; 62,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,88; 63,27</t>
+          <t>12,82; 58,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,9; 53,97</t>
+          <t>20,66; 51,55</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,67; 40,91</t>
+          <t>26,45; 39,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27,14; 39,18</t>
+          <t>32,67; 46,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,73; 37,66</t>
+          <t>31,19; 40,36</t>
         </is>
       </c>
     </row>
@@ -927,18 +927,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>23908</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6324; 14177</t>
+          <t>8927; 18202</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9741; 19894</t>
+          <t>6592; 14383</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19088; 31364</t>
+          <t>17617; 29916</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15856</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5265; 12843</t>
+          <t>3529; 11306</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3819; 12119</t>
+          <t>5081; 12588</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11112; 21615</t>
+          <t>10548; 22199</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8467</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1598; 6244</t>
+          <t>1792; 8079</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1929; 9362</t>
+          <t>1785; 6635</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4719; 13428</t>
+          <t>4885; 12659</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>17357</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>29703</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6090; 32432</t>
+          <t>7786; 18169</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9370; 20952</t>
+          <t>12142; 22671</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16857; 49245</t>
+          <t>22705; 38333</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>21590</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7347; 16339</t>
+          <t>5842; 15472</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6183; 16322</t>
+          <t>7022; 16234</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16241; 29294</t>
+          <t>15629; 28729</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9698</t>
+          <t>9532</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1589; 7185</t>
+          <t>2096; 8804</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2430; 9679</t>
+          <t>1596; 7309</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5476; 14853</t>
+          <t>5487; 13693</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34824; 72420</t>
+          <t>43130; 64806</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48794; 70461</t>
+          <t>46517; 65699</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88258; 134394</t>
+          <t>95262; 123271</t>
         </is>
       </c>
     </row>
